--- a/reports/一级子公司A_利润表_2025-08.xlsx
+++ b/reports/一级子公司A_利润表_2025-08.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>191640210</v>
+        <v>196139857</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>186726221</v>
+        <v>186991114</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1344124552</v>
+        <v>1344575505</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>764999</v>
+        <v>757712</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>5482385</v>
+        <v>5478547</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>661623</v>
+        <v>658085</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4756589</v>
+        <v>4753586</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>562224</v>
+        <v>558648</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>4030874</v>
+        <v>4028840</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>514218</v>
+        <v>515037</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3708014</v>
+        <v>3707061</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>280353</v>
+        <v>280539</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2014987</v>
+        <v>2015059</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>222999</v>
+        <v>224847</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1611826</v>
+        <v>1612314</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>188633794</v>
+        <v>193144989</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>183719805</v>
+        <v>183996246</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>94151546</v>
+        <v>95188582</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>680770272</v>
+        <v>681376297</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1731411</v>
+        <v>1743097</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>12489276</v>
+        <v>12497848</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1563972</v>
+        <v>1569668</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>11282130</v>
+        <v>11286234</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>84407361</v>
+        <v>83657743</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>604513143</v>
+        <v>604376575</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1785569</v>
+        <v>1783839</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>12896244</v>
+        <v>12892536</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>788339</v>
+        <v>780110</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>5642693</v>
+        <v>5640157</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2791115</v>
+        <v>2785232</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>20151937</v>
+        <v>20141329</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1238319</v>
+        <v>1225940</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>8868133</v>
+        <v>8862377</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4823821</v>
+        <v>4797396</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>34667330</v>
+        <v>34645184</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>90168</v>
+        <v>89829</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>720038</v>
+        <v>719948</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2554752</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>18375195</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1706766</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>12252231</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>127803378</v>
+        <v>137705167</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>114312928</v>
+        <v>114939020</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>111973778</v>
+        <v>112576622</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>805811133</v>
+        <v>806328461</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2339150</v>
+        <v>2362398</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>16921660</v>
+        <v>16932678</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4267141</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>30637175</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1362618</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>9802516</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>849767</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>6125539</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1017781</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>7349418</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>762364</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>5511317</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>508030</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>3673915</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>423576</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3061561</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1970214</v>
+        <v>1953429</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>14108130</v>
+        <v>14100170</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1509690</v>
+        <v>1509860</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>10882790</v>
+        <v>10878585</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1234832</v>
+        <v>1232785</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>8866583</v>
+        <v>8865350</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>9267988</v>
+        <v>9321501</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>66897012</v>
+        <v>66904677</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349389</v>
+        <v>393669</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2799344</v>
+        <v>2821686</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>668027</v>
+        <v>673486</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>5358879</v>
+        <v>5362088</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>756869</v>
+        <v>673486</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>6078517</v>
+        <v>5362088</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>89896</v>
+        <v>90377</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>719878</v>
+        <v>720191</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>342806</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2736300</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>744961</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>5360637</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>227553</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1823624</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>170352</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1367556</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>283587</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2279123</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1058413</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>7653944</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>151298</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1215632</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>113638</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>911838</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>189777</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1519972</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>133138</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1064153</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>95291</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>760212</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>76346</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>608222</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>57299</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>456179</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>60830416</v>
+        <v>57964621</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>70326505</v>
+        <v>65069834</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>426489</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3063616</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>94992</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>759941</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>150337</v>
+        <v>149670</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1200152</v>
+        <v>1199732</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>60680079</v>
+        <v>58241440</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5329055</v>
+        <v>5273245</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>42410012</v>
+        <v>42383578</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>55351024</v>
+        <v>52968195</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>55351024</v>
+        <v>52968195</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>55351024</v>
+        <v>52968195</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>55351024</v>
+        <v>52968195</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>55351024</v>
+        <v>52968195</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
